--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-15321</t>
+          <t>I-15321</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-15352</t>
+          <t>I-254583</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.0642985</t>
+          <t>-12.074111</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.1121293</t>
+          <t>-77.1226195</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida República de Venezuela / Calle Baca Flor</t>
+          <t>Avenida Costanera / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-18594</t>
+          <t>I-257103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.0657679</t>
+          <t>-12.0658437</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-77.1213555</t>
+          <t>-77.1217727</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida José Gálvez / Calle Iquique / Jr. Arica / Jr. Colina</t>
+          <t>Avenida José Gálvez / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-18632</t>
+          <t>I-554305</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.0657188</t>
+          <t>-12.0644903</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-77.1210832</t>
+          <t>-77.1124692</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida José Gálvez</t>
+          <t>Avenida República de Venezuela / Calle Carlos Saco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-252038</t>
+          <t>I-14984</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.0680386</t>
+          <t>-12.0644814</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.1148451</t>
+          <t>-77.1083875</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida de La Marina</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Calle Elias Chunga Zapata</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-254583</t>
+          <t>I-15377</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.074111</t>
+          <t>-12.0731632</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.1226195</t>
+          <t>-77.1213888</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Costanera</t>
+          <t>Avenida La Paz / Calle España</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-254584</t>
+          <t>I-15400</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.0747504</t>
+          <t>-12.0692907</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.1210428</t>
+          <t>-77.1124733</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Costanera</t>
+          <t>Avenida de La Marina / Calle Huamachuco</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-254586</t>
+          <t>I-254028</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.0741764</t>
+          <t>-12.0728025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-77.1224516</t>
+          <t>-77.1119227</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Costanera</t>
+          <t>Avenida El Pacífico / Avenida Víctor Raúl Haya de la Torre</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-257103</t>
+          <t>I-550311</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.0658437</t>
+          <t>-12.0764883</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-77.1217727</t>
+          <t>-77.1132437</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida José Gálvez</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Avenida La Paz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-381944</t>
+          <t>I-749372</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.0645064</t>
+          <t>-12.0744562</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-77.1120933</t>
+          <t>-77.1206546</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle Baca Flor</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-381945</t>
+          <t>I-5747</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.0643897</t>
+          <t>-12.063563</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-77.1121135</t>
+          <t>-77.1087055</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle Baca Flor</t>
+          <t>Avenida República de Venezuela / Avenida Víctor Raúl Haya de la Torre</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-391640</t>
+          <t>I-252006</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.0645567</t>
+          <t>-12.0703341</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-77.1122482</t>
+          <t>-77.1089364</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-554304</t>
+          <t>I-252018</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1132,22 +1132,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-12.0644437</t>
+          <t>-12.0698644</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-77.1122591</t>
+          <t>-77.1159746</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Callao / Calle Mariscal Castilla</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-554305</t>
+          <t>I-252051</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.0644903</t>
+          <t>-12.0711018</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-77.1124692</t>
+          <t>-77.1083633</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida El Pacífico / Avenida de La Marina</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-5746</t>
+          <t>I-253348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.0641616</t>
+          <t>-12.0675093</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-77.1121508</t>
+          <t>-77.1156502</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Calle Baca Flor</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-5748</t>
+          <t>I-253354</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.0647558</t>
+          <t>-12.0667042</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-77.1155314</t>
+          <t>-77.1140426</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela</t>
+          <t>Calle Las Amatistas / Calle Los Opalos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-749372</t>
+          <t>I-253838</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,22 +1340,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-12.0744562</t>
+          <t>-12.0632044</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.1206546</t>
+          <t>-77.1052471</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida República de Venezuela / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>l-750141</t>
+          <t>I-252008</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.0659138</t>
+          <t>-12.0709313</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-77.1217588</t>
+          <t>-77.1073944</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l-762425</t>
+          <t>I-5749</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.0738279</t>
+          <t>-12.0645785</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-77.1227975</t>
+          <t>-77.114551</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle Tacna</t>
+          <t>Avenida República de Venezuela / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>l-768202</t>
+          <t>I-251412</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1496,22 +1496,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.0746698</t>
+          <t>-12.0709222</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.1209006</t>
+          <t>-77.1302258</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Costanera / Jirón Alfonso Ugarte</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>l-774831</t>
+          <t>I-251414</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1548,22 +1548,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.0747274</t>
+          <t>-12.0688429</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.1210367</t>
+          <t>-77.1294558</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Jirón Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>l-787419</t>
+          <t>I-251416</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1600,22 +1600,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-12.0643223</t>
+          <t>-12.0671738</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-77.1122622</t>
+          <t>-77.128827</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida República de Venezuela</t>
+          <t>Jirón Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>l-787420</t>
+          <t>I-251417</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1652,233 +1652,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-12.0643627</t>
+          <t>-12.0699769</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.1124878</t>
+          <t>-77.1298828</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida República de Venezuela</t>
+          <t>Jirón Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>l-824945</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-12.0642675</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-77.1119563</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Auxiliar Avenida República de Venezuela</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-828175</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-12.0740692</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-77.1224063</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-91122</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-12.0740041</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-77.1228939</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Avenida Costanera / Calle Tacna</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>l-91123</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-12.0739165</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-77.122846</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Calle Tacna</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
         <is>
           <t>070104</t>
         </is>

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1676,6 +1676,266 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-6202</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-12.077664</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-77.1136493</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Avenida Costanera / Avenida Víctor Raúl Haya de la Torre</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-301349</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-12.075876</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-77.1143102</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Avenida La Paz / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-18667</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-12.0684247</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-77.1320316</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jirón Huascar / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-18669</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-12.0695142</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-77.1317221</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Avenida La Paz / Jirón Francisco Bolognesi</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-18670</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-12.069187</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-77.1326322</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Avenida La Paz / Jirón Víctor Fajardo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,7 +674,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Calle Carlos Saco</t>
+          <t>Auxiliar Avenida República de Venezuela / Calle Carlos Saco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Víctor Raúl Haya de la Torre / Avenida La Paz</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Avenida Víctor Raúl Haya de la Torre</t>
+          <t>Auxiliar Avenida República de Venezuela / Avenida República de Venezuela / Avenida Víctor Raúl Haya de la Torre / Avenida del Pescador</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I-253838</t>
+          <t>I-252008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-12.0632044</t>
+          <t>-12.0709313</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.1052471</t>
+          <t>-77.1073944</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Calle s / n</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I-252008</t>
+          <t>I-5749</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.0709313</t>
+          <t>-12.0645785</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-77.1073944</t>
+          <t>-77.114551</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida de La Marina / Calle s / n</t>
+          <t>Avenida República de Venezuela / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I-5749</t>
+          <t>I-251412</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.0645785</t>
+          <t>-12.0709222</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-77.114551</t>
+          <t>-77.1302258</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Calle s / n</t>
+          <t>Avenida Costanera / Jirón Alfonso Ugarte</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I-251412</t>
+          <t>I-251414</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.0709222</t>
+          <t>-12.0688429</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.1302258</t>
+          <t>-77.1294558</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Avenida Costanera / Jirón Alfonso Ugarte</t>
+          <t>Jirón Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I-251414</t>
+          <t>I-251416</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1548,17 +1548,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.0688429</t>
+          <t>-12.0671738</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.1294558</t>
+          <t>-77.128827</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jirón Alfonso Ugarte / Calle s / n</t>
+          <t>Avenida José Gálvez / Calle Alfonso Ugarte / Jirón Alfonso Ugarte</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I-251416</t>
+          <t>I-251417</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-12.0671738</t>
+          <t>-12.0699769</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-77.128827</t>
+          <t>-77.1298828</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I-251417</t>
+          <t>I-6202</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-12.0699769</t>
+          <t>-12.077664</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.1298828</t>
+          <t>-77.1136493</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jirón Alfonso Ugarte / Calle s / n</t>
+          <t>Avenida Costanera / Avenida Víctor Raúl Haya de la Torre</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I-6202</t>
+          <t>I-301349</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-12.077664</t>
+          <t>-12.075876</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-77.1136493</t>
+          <t>-77.1143102</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avenida Costanera / Avenida Víctor Raúl Haya de la Torre</t>
+          <t>Avenida La Paz / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>I-301349</t>
+          <t>I-18667</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1756,17 +1756,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-12.075876</t>
+          <t>-12.0684247</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-77.1143102</t>
+          <t>-77.1320316</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Calle s / n</t>
+          <t>Jirón Huascar / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I-18667</t>
+          <t>I-18669</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-12.0684247</t>
+          <t>-12.0695142</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.1320316</t>
+          <t>-77.1317221</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Jirón Huascar / Calle s / n</t>
+          <t>Avenida La Paz / Jirón Francisco Bolognesi</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>I-18669</t>
+          <t>I-18670</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.0695142</t>
+          <t>-12.069187</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-77.1317221</t>
+          <t>-77.1326322</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Jirón Francisco Bolognesi</t>
+          <t>Avenida La Paz / Jirón Víctor Fajardo</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>I-18670</t>
+          <t>I-6206</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-12.069187</t>
+          <t>-12.0750052</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-77.1326322</t>
+          <t>-77.1125893</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Jirón Víctor Fajardo</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Jirón Atahualpa / Jirón Libertad</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1931,6 +1931,682 @@
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-18622</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-12.0675138</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-77.1271352</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Calle Washington / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-18615</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-12.0702766</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-77.1280358</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Calle 8 de Octubre / Calle Washington</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>I-18617</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-12.0690675</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-77.1275539</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Calle Washington / Jirón Atahualpa</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I-18618</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-12.0707781</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-77.1282211</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Avenida La Paz / Calle Washington</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>I-15288</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-12.0703371</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-77.1114774</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Calle Mantaro / Calle Talara</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>I-15360</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-12.0694422</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-77.11688</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Calle Mama Ocllo / Calle Mariscal Castilla</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>I-15379</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-12.0744753</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-77.1178223</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Avenida Callao / Avenida La Paz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>I-15454</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-12.0722944</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-77.1136842</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Avenida El Pacífico / Calle Huamachuco / Jirón Huamachuco</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>I-15653</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-12.0731675</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-77.1105845</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Avenida El Pacífico / Calle Valencia</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>I-251423</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-12.0720745</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-77.1207686</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Calle España / Jirón Atahualpa</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>I-252019</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-12.0680036</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-77.1195021</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Calle Mariscal Castilla / Calle Tacna</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>I-298591</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-12.0711259</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-77.1164989</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Avenida Callao / Avenida El Pacífico</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>I-373704</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-12.0758378</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-77.1105158</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Calle Emancipación / Jirón Libertad</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>070104</t>
         </is>

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-15321</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.0667502</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-254583</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.074111</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-257103</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.0658437</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-554305</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.0644903</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-14984</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.0644814</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-15377</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.0731632</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-15400</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.0692907</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-254028</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.0728025</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-550311</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.0764883</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-749372</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-12.0744562</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-5747</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-12.063563</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-252006</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-12.0703341</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-252018</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-12.0698644</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-252051</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-12.0711018</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-253348</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-12.0675093</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-253354</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-12.0667042</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-252008</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-12.0709313</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-5749</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-12.0645785</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-251412</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-12.0709222</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-251414</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-12.0688429</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-251416</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-12.0671738</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-251417</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-12.0699769</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-6202</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-12.077664</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-301349</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-12.075876</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-18667</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-12.0684247</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-18669</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-12.0695142</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-18670</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-12.069187</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-6206</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-12.0750052</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-18622</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-12.0675138</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-18615</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-12.0702766</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-18617</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-12.0690675</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-18618</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-12.0707781</t>
@@ -2136,40 +1976,35 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>I-15288</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-12.0703371</t>
@@ -2188,40 +2023,35 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>I-15360</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-12.0694422</t>
@@ -2240,40 +2070,35 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>I-15379</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-12.0744753</t>
@@ -2292,40 +2117,35 @@
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>I-15454</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-12.0722944</t>
@@ -2344,40 +2164,35 @@
       <c r="I37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>I-15653</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-12.0731675</t>
@@ -2396,40 +2211,35 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>I-251423</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-12.0720745</t>
@@ -2448,40 +2258,35 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>I-252019</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-12.0680036</t>
@@ -2500,40 +2305,35 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>I-298591</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-12.0711259</t>
@@ -2552,40 +2352,35 @@
       <c r="I41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LA_PERLA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>I-373704</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>070104</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-12.0758378</t>
@@ -2604,11 +2399,6 @@
       <c r="I42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>070104</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LA_PERLA</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2390,6 +2390,711 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>I-15131</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-12.0684729</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-77.1267069</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Calle Abraham Lincoln / Jirón Cahuide</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>I-15646</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-12.0740094</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-77.1109336</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Calle Alipio Ponce / Calle José Abelardo Quiñones</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>I-15301</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-12.0666109</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-77.1105387</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Calle Ignacio Merino Muñóz / Calle José Carlos Mariátegui</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>I-15409</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-12.0721627</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-77.1121856</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Calle Lambayeque / Calle Ucayali</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>I-15410</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-12.0714492</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-77.1115384</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Calle Lambayeque / Calle Amazonas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>I-15618</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-12.0755537</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-77.1102839</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Calle Emancipación / Calle Heraldos Negros</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>I-15367</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-12.0718501</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-77.1200898</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Jirón Cahuide / Calle Wiracocha</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>I-15152</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-12.0712154</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-77.1242695</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jirón Huascar / Jirón Tarata</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>I-15422</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-12.0722181</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-77.1153398</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Calle Junin / Calle Tumbes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>I-15179</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-12.0705701</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-77.1188091</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Calle Pachacútec / Calle Mariano Melgar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>I-15194</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-12.07011</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-77.1196495</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Jirón España / Calle Mariano Melgar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>I-15311</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-12.0681395</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-77.111051</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Calle José Maria Eguren / Calle Carlos Baca Flor Falcon</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>I-18666</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-12.068322</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-77.1323161</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Jirón Huascar / Jirón Víctor Fajardo</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>I-13551</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-12.069291</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-77.1296237</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Jirón Alfonso Ugarte / Jirón Huascar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>070104</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LA PERLA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>I-16911</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-12.0678516</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-77.1270787</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Jirón Washington / Jirón Unión</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -1196,17 +1196,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.0667042</t>
+          <t>-12.0674219</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-77.1140426</t>
+          <t>-77.1075536</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle Las Amatistas / Calle Los Opalos</t>
+          <t>Calle Cumana / Calle Vinzos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">

--- a/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
+++ b/Intersecciones/excels/CALLAO-CALLAO-LA_PERLA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-15321</t>
+          <t>I-749372</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.0667502</t>
+          <t>-12.0744562</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.1120697</t>
+          <t>-77.1206546</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle Carlos Saco / Calle Manuel Ascencio Segura</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-254583</t>
+          <t>I-6206</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.074111</t>
+          <t>-12.0750052</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.1226195</t>
+          <t>-77.1125893</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Costanera / Calle s / n</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Jirón Libertad</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-257103</t>
+          <t>I-6202</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.0658437</t>
+          <t>-12.077664</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-77.1217727</t>
+          <t>-77.1136493</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida José Gálvez / Calle s / n</t>
+          <t>Avenida Costanera / Avenida Víctor Raúl Haya de la Torre</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-554305</t>
+          <t>I-5749</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.0644903</t>
+          <t>-12.0645785</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-77.1124692</t>
+          <t>-77.114551</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida República de Venezuela / Calle Carlos Saco</t>
+          <t>Avenida República de Venezuela / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-14984</t>
+          <t>I-5747</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.0644814</t>
+          <t>-12.063563</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.1083875</t>
+          <t>-77.1087055</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Víctor Raúl Haya de la Torre / Calle Elias Chunga Zapata</t>
+          <t>Avenida República de Venezuela / Avenida Víctor Raúl Haya de la Torre</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-15377</t>
+          <t>I-554305</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.0731632</t>
+          <t>-12.0644903</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.1213888</t>
+          <t>-77.1124692</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Calle España</t>
+          <t>Avenida República de Venezuela / Calle Carlos Saco</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-15400</t>
+          <t>I-550311</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.0692907</t>
+          <t>-12.0764883</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.1124733</t>
+          <t>-77.1132437</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida de La Marina / Calle Huamachuco</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Avenida La Paz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-254028</t>
+          <t>I-373704</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.0728025</t>
+          <t>-12.0758378</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-77.1119227</t>
+          <t>-77.1105158</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida El Pacífico / Avenida Víctor Raúl Haya de la Torre</t>
+          <t>Calle Emancipación / Jirón Libertad</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-550311</t>
+          <t>I-301349</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.0764883</t>
+          <t>-12.075876</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-77.1132437</t>
+          <t>-77.1143102</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Víctor Raúl Haya de la Torre / Calle s / n</t>
+          <t>Avenida La Paz / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,27 +909,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-749372</t>
+          <t>I-298591</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.0744562</t>
+          <t>-12.0711259</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-77.1206546</t>
+          <t>-77.1164989</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Callao / Avenida El Pacífico</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-5747</t>
+          <t>I-257103</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.063563</t>
+          <t>-12.0658437</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-77.1087055</t>
+          <t>-77.1217727</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida República de Venezuela / Avenida República de Venezuela / Avenida Víctor Raúl Haya de la Torre / Avenida del Pescador</t>
+          <t>Avenida José Gálvez / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1003,27 +1003,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-252006</t>
+          <t>I-254583</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.0703341</t>
+          <t>-12.074111</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-77.1089364</t>
+          <t>-77.1226195</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida de La Marina / Calle s / n</t>
+          <t>Avenida Costanera / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-252018</t>
+          <t>I-254028</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-12.0698644</t>
+          <t>-12.0728025</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-77.1159746</t>
+          <t>-77.1119227</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Callao / Calle Mariscal Castilla</t>
+          <t>Avenida El Pacífico / Avenida Víctor Raúl Haya de la Torre</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-252051</t>
+          <t>I-253354</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.0711018</t>
+          <t>-12.0674219</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-77.1083633</t>
+          <t>-77.1075536</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida El Pacífico / Avenida de La Marina</t>
+          <t>Calle Cumana / Calle Vinzos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-253354</t>
+          <t>I-252051</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.0674219</t>
+          <t>-12.0711018</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-77.1075536</t>
+          <t>-77.1083633</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle Cumana / Calle Vinzos</t>
+          <t>Avenida El Pacífico / Avenida de La Marina</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-252008</t>
+          <t>I-252019</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-12.0709313</t>
+          <t>-12.0680036</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.1073944</t>
+          <t>-77.1195021</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida de La Marina / Calle s / n</t>
+          <t>Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-5749</t>
+          <t>I-252018</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.0645785</t>
+          <t>-12.0698644</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-77.114551</t>
+          <t>-77.1159746</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Calle s / n</t>
+          <t>Avenida Callao / Calle Mariscal Castilla</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-251412</t>
+          <t>I-252008</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.0709222</t>
+          <t>-12.0709313</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-77.1302258</t>
+          <t>-77.1073944</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida Costanera / Jirón Alfonso Ugarte</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-251414</t>
+          <t>I-252006</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.0688429</t>
+          <t>-12.0703341</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.1294558</t>
+          <t>-77.1089364</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jirón Alfonso Ugarte / Calle s / n</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-251416</t>
+          <t>I-251423</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.0671738</t>
+          <t>-12.0720745</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.128827</t>
+          <t>-77.1207686</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida José Gálvez / Calle Alfonso Ugarte / Jirón Alfonso Ugarte</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-6202</t>
+          <t>I-251416</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-12.077664</t>
+          <t>-12.0671738</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.1136493</t>
+          <t>-77.128827</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Avenida Costanera / Avenida Víctor Raúl Haya de la Torre</t>
+          <t>Jirón Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-301349</t>
+          <t>I-251414</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-12.075876</t>
+          <t>-12.0688429</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-77.1143102</t>
+          <t>-77.1294558</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Calle s / n</t>
+          <t>Jirón Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-18667</t>
+          <t>I-251412</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-12.0684247</t>
+          <t>-12.0709222</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-77.1320316</t>
+          <t>-77.1302258</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Jirón Huascar / Calle s / n</t>
+          <t>Avenida Costanera / Jirón Alfonso Ugarte</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-18669</t>
+          <t>I-18670</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-12.0695142</t>
+          <t>-12.069187</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.1317221</t>
+          <t>-77.1326322</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Jirón Francisco Bolognesi</t>
+          <t>Avenida La Paz / Jirón Víctor Fajardo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-18670</t>
+          <t>I-18669</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.069187</t>
+          <t>-12.0695142</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-77.1326322</t>
+          <t>-77.1317221</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Jirón Víctor Fajardo</t>
+          <t>Avenida La Paz / Jirón Francisco Bolognesi</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-6206</t>
+          <t>I-18667</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-12.0750052</t>
+          <t>-12.0684247</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-77.1125893</t>
+          <t>-77.1320316</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida Víctor Raúl Haya de la Torre / Jirón Atahualpa / Jirón Libertad</t>
+          <t>Jirón Huascar / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-18622</t>
+          <t>I-18666</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-12.0675138</t>
+          <t>-12.068322</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-77.1271352</t>
+          <t>-77.1323161</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Calle Washington / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-18615</t>
+          <t>I-18622</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-12.0702766</t>
+          <t>-12.0675138</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-77.1280358</t>
+          <t>-77.1271352</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Calle 8 de Octubre / Calle Washington</t>
+          <t>Calle Washington / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-18617</t>
+          <t>I-18618</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-12.0690675</t>
+          <t>-12.0707781</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-77.1275539</t>
+          <t>-77.1282211</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Calle Washington / Jirón Atahualpa</t>
+          <t>Avenida La Paz / Calle Washington</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-18618</t>
+          <t>I-18617</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-12.0707781</t>
+          <t>-12.0690675</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-77.1282211</t>
+          <t>-77.1275539</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Calle Washington</t>
+          <t>Calle Washington / Jirón Atahualpa</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-15288</t>
+          <t>I-18615</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-12.0703371</t>
+          <t>-12.0702766</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-77.1114774</t>
+          <t>-77.1280358</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Calle Mantaro / Calle Talara</t>
+          <t>Calle 8 de Octubre / Calle Washington</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-15360</t>
+          <t>I-16911</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-12.0694422</t>
+          <t>-12.0678516</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-77.11688</t>
+          <t>-77.1270787</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Calle Mama Ocllo / Calle Mariscal Castilla</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2084,22 +2084,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-15379</t>
+          <t>I-15653</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-12.0744753</t>
+          <t>-12.0731675</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-77.1178223</t>
+          <t>-77.1105845</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Avenida Callao / Avenida La Paz</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-15454</t>
+          <t>I-15646</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-12.0722944</t>
+          <t>-12.0740094</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-77.1136842</t>
+          <t>-77.1109336</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Avenida El Pacífico / Calle Huamachuco / Jirón Huamachuco</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-15653</t>
+          <t>I-15618</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-12.0731675</t>
+          <t>-12.0755537</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-77.1105845</t>
+          <t>-77.1102839</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Avenida El Pacífico / Calle Valencia</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-251423</t>
+          <t>I-15454</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-12.0720745</t>
+          <t>-12.0722944</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-77.1207686</t>
+          <t>-77.1136842</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Calle España / Jirón Atahualpa</t>
+          <t>Avenida El Pacífico / Calle Huamachuco / Jirón Huamachuco</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I-252019</t>
+          <t>I-15422</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-12.0680036</t>
+          <t>-12.0722181</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-77.1195021</t>
+          <t>-77.1153398</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Calle Mariscal Castilla / Calle Tacna</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-298591</t>
+          <t>I-15410</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-12.0711259</t>
+          <t>-12.0714492</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-77.1164989</t>
+          <t>-77.1115384</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Avenida Callao / Avenida El Pacífico</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I-373704</t>
+          <t>I-15409</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-12.0758378</t>
+          <t>-12.0721627</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-77.1105158</t>
+          <t>-77.1121856</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Calle Emancipación / Jirón Libertad</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I-15131</t>
+          <t>I-15400</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-12.0684729</t>
+          <t>-12.0692907</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-77.1267069</t>
+          <t>-77.1124733</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Calle Abraham Lincoln / Jirón Cahuide</t>
+          <t>Avenida de La Marina / Calle Huamachuco</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2460,22 +2460,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>I-15646</t>
+          <t>I-15379</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-12.0740094</t>
+          <t>-12.0744753</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-77.1109336</t>
+          <t>-77.1178223</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Calle Alipio Ponce / Calle José Abelardo Quiñones</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2507,22 +2507,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>I-15301</t>
+          <t>I-15377</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-12.0666109</t>
+          <t>-12.0731632</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-77.1105387</t>
+          <t>-77.1213888</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Calle Ignacio Merino Muñóz / Calle José Carlos Mariátegui</t>
+          <t>Avenida La Paz / Calle España</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>I-15409</t>
+          <t>I-15367</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-12.0721627</t>
+          <t>-12.0718501</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-77.1121856</t>
+          <t>-77.1200898</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Calle Lambayeque / Calle Ucayali</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I-15410</t>
+          <t>I-15360</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-12.0714492</t>
+          <t>-12.0694422</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-77.1115384</t>
+          <t>-77.11688</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Calle Lambayeque / Calle Amazonas</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2648,27 +2648,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I-15618</t>
+          <t>I-15321</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-12.0755537</t>
+          <t>-12.0667502</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-77.1102839</t>
+          <t>-77.1120697</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Calle Emancipación / Calle Heraldos Negros</t>
+          <t>Calle Carlos Saco / Calle Manuel Ascencio Segura</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2695,22 +2695,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>I-15367</t>
+          <t>I-15311</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-12.0718501</t>
+          <t>-12.0681395</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-77.1200898</t>
+          <t>-77.111051</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Jirón Cahuide / Calle Wiracocha</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2742,22 +2742,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I-15152</t>
+          <t>I-15301</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-12.0712154</t>
+          <t>-12.0666109</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-77.1242695</t>
+          <t>-77.1105387</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Jirón Huascar / Jirón Tarata</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2789,22 +2789,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I-15422</t>
+          <t>I-15288</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-12.0722181</t>
+          <t>-12.0703371</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-77.1153398</t>
+          <t>-77.1114774</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Calle Junin / Calle Tumbes</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>I-15179</t>
+          <t>I-15194</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-12.0705701</t>
+          <t>-12.07011</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-77.1188091</t>
+          <t>-77.1196495</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Calle Pachacútec / Calle Mariano Melgar</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2883,22 +2883,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>I-15194</t>
+          <t>I-15179</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-12.07011</t>
+          <t>-12.0705701</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-77.1196495</t>
+          <t>-77.1188091</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Jirón España / Calle Mariano Melgar</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2930,22 +2930,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>I-15311</t>
+          <t>I-15152</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-12.0681395</t>
+          <t>-12.0712154</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-77.111051</t>
+          <t>-77.1242695</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Calle José Maria Eguren / Calle Carlos Baca Flor Falcon</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>I-18666</t>
+          <t>I-15131</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-12.068322</t>
+          <t>-12.0684729</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-77.1323161</t>
+          <t>-77.1267069</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jirón Huascar / Jirón Víctor Fajardo</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3024,22 +3024,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>I-13551</t>
+          <t>I-14984</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-12.069291</t>
+          <t>-12.0644814</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-77.1296237</t>
+          <t>-77.1083875</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Jirón Alfonso Ugarte / Jirón Huascar</t>
+          <t>Avenida Víctor Raúl Haya de la Torre / Calle Elias Chunga Zapata</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3071,22 +3071,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>I-16911</t>
+          <t>I-13551</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-12.0678516</t>
+          <t>-12.069291</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-77.1270787</t>
+          <t>-77.1296237</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Jirón Washington / Jirón Unión</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
